--- a/zobba/fixtures/documents/AP population.xlsx
+++ b/zobba/fixtures/documents/AP population.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mismatch" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edge" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lines" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dated" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="000000"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd hh:mm"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -52,10 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -45710,4 +45719,468 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Invoice date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Approved before payment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Approved at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>46086</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>46086.4375</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>46006.375</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>INV-D3</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>46113.34375</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>